--- a/informes/socios.xlsx
+++ b/informes/socios.xlsx
@@ -234,7 +234,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1783275965" name="Picture">
+        <xdr:cNvPr id="57301692" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -432,7 +432,7 @@
       <c r="M6" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">miércoles 27 mayo 2026</t>
+            <t xml:space="preserve">domingo 31 mayo 2026</t>
           </r>
         </is>
       </c>
@@ -591,7 +591,7 @@
       <c r="N10" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">15/1/23, 0:00</t>
+            <t xml:space="preserve">15/01/23 0:00</t>
           </r>
         </is>
       </c>
@@ -650,7 +650,7 @@
       <c r="N11" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">10/2/23, 0:00</t>
+            <t xml:space="preserve">10/02/23 0:00</t>
           </r>
         </is>
       </c>
@@ -709,7 +709,7 @@
       <c r="N12" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">5/3/23, 0:00</t>
+            <t xml:space="preserve">5/03/23 0:00</t>
           </r>
         </is>
       </c>
@@ -768,7 +768,7 @@
       <c r="N13" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/4/23, 0:00</t>
+            <t xml:space="preserve">1/04/23 0:00</t>
           </r>
         </is>
       </c>
@@ -827,7 +827,7 @@
       <c r="N14" s="7" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">20/5/23, 0:00</t>
+            <t xml:space="preserve">20/05/23 0:00</t>
           </r>
         </is>
       </c>
@@ -845,92 +845,933 @@
       <c r="T14" s="7" t="inlineStr"/>
       <c r="U14" s="1" t="inlineStr"/>
     </row>
-    <row r="15" customHeight="1" ht="142">
+    <row r="15" customHeight="1" ht="30">
       <c r="A15" s="1" t="inlineStr"/>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr"/>
-      <c r="D15" s="1" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">asad a a</t>
+          </r>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr"/>
-      <c r="G15" s="1" t="inlineStr"/>
-      <c r="H15" s="1" t="inlineStr"/>
-      <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr"/>
-      <c r="L15" s="1" t="inlineStr"/>
-      <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
-      <c r="O15" s="1" t="inlineStr"/>
-      <c r="P15" s="1" t="inlineStr"/>
-      <c r="Q15" s="1" t="inlineStr"/>
-      <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
-      <c r="T15" s="1" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">12345555</t>
+          </r>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">67777777</t>
+          </r>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">a@a.com</t>
+          </r>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">31/05/26 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Baja</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
     </row>
     <row r="16" customHeight="1" ht="30">
       <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr"/>
-      <c r="D16" s="1" t="inlineStr"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Juan a a</t>
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="1" t="inlineStr"/>
       <c r="F16" s="1" t="inlineStr"/>
-      <c r="G16" s="1" t="inlineStr"/>
-      <c r="H16" s="1" t="inlineStr"/>
-      <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr"/>
-      <c r="L16" s="1" t="inlineStr"/>
-      <c r="M16" s="1" t="inlineStr"/>
-      <c r="N16" s="1" t="inlineStr"/>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">1</t>
-          </r>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr"/>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">/</t>
-          </r>
-        </is>
-      </c>
-      <c r="R16" s="8" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">1</t>
-          </r>
-        </is>
-      </c>
-      <c r="S16" s="8" t="inlineStr"/>
-      <c r="T16" s="8" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">a</t>
+          </r>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">655443344</t>
+          </r>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">a@.com</t>
+          </r>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">31/05/26 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Baja</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
     </row>
-    <row r="17" customHeight="1" ht="40">
+    <row r="17" customHeight="1" ht="30">
       <c r="A17" s="1" t="inlineStr"/>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr"/>
-      <c r="D17" s="1" t="inlineStr"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr"/>
-      <c r="G17" s="1" t="inlineStr"/>
-      <c r="H17" s="1" t="inlineStr"/>
-      <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr"/>
-      <c r="L17" s="1" t="inlineStr"/>
-      <c r="M17" s="1" t="inlineStr"/>
-      <c r="N17" s="1" t="inlineStr"/>
-      <c r="O17" s="1" t="inlineStr"/>
-      <c r="P17" s="1" t="inlineStr"/>
-      <c r="Q17" s="1" t="inlineStr"/>
-      <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
-      <c r="T17" s="1" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11223344F</t>
+          </r>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">611000001</t>
+          </r>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javier.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr"/>
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="7" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" customHeight="1" ht="52">
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr"/>
+      <c r="F18" s="1" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr"/>
+      <c r="H18" s="1" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr"/>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
+      <c r="L18" s="1" t="inlineStr"/>
+      <c r="M18" s="1" t="inlineStr"/>
+      <c r="N18" s="1" t="inlineStr"/>
+      <c r="O18" s="1" t="inlineStr"/>
+      <c r="P18" s="1" t="inlineStr"/>
+      <c r="Q18" s="1" t="inlineStr"/>
+      <c r="R18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr"/>
+      <c r="T18" s="1" t="inlineStr"/>
+      <c r="U18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" customHeight="1" ht="30">
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr"/>
+      <c r="D19" s="1" t="inlineStr"/>
+      <c r="E19" s="1" t="inlineStr"/>
+      <c r="F19" s="1" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr"/>
+      <c r="H19" s="1" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr"/>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
+      <c r="L19" s="1" t="inlineStr"/>
+      <c r="M19" s="1" t="inlineStr"/>
+      <c r="N19" s="1" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1</t>
+          </r>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr"/>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">/</t>
+          </r>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2</t>
+          </r>
+        </is>
+      </c>
+      <c r="S19" s="8" t="inlineStr"/>
+      <c r="T19" s="8" t="inlineStr"/>
+      <c r="U19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" customHeight="1" ht="40">
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr"/>
+      <c r="D20" s="1" t="inlineStr"/>
+      <c r="E20" s="1" t="inlineStr"/>
+      <c r="F20" s="1" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr"/>
+      <c r="H20" s="1" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
+      <c r="L20" s="1" t="inlineStr"/>
+      <c r="M20" s="1" t="inlineStr"/>
+      <c r="N20" s="1" t="inlineStr"/>
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="1" t="inlineStr"/>
+      <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr"/>
+      <c r="S20" s="1" t="inlineStr"/>
+      <c r="T20" s="1" t="inlineStr"/>
+      <c r="U20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" customHeight="1" ht="55">
+      <c r="A21" s="1" t="inlineStr"/>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr"/>
+      <c r="D21" s="1" t="inlineStr"/>
+      <c r="E21" s="1" t="inlineStr"/>
+      <c r="F21" s="1" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr"/>
+      <c r="H21" s="1" t="inlineStr"/>
+      <c r="I21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
+      <c r="L21" s="1" t="inlineStr"/>
+      <c r="M21" s="1" t="inlineStr"/>
+      <c r="N21" s="1" t="inlineStr"/>
+      <c r="O21" s="1" t="inlineStr"/>
+      <c r="P21" s="1" t="inlineStr"/>
+      <c r="Q21" s="1" t="inlineStr"/>
+      <c r="R21" s="1" t="inlineStr"/>
+      <c r="S21" s="1" t="inlineStr"/>
+      <c r="T21" s="1" t="inlineStr"/>
+      <c r="U21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" customHeight="1" ht="30">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Nombre</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DNI</t>
+          </r>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Telefono</t>
+          </r>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Correo</t>
+          </r>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Fecha_Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Estado</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr"/>
+      <c r="U22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" customHeight="1" ht="31">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr"/>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+      <c r="G23" s="1" t="inlineStr"/>
+      <c r="H23" s="1" t="inlineStr"/>
+      <c r="I23" s="1" t="inlineStr"/>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
+      <c r="L23" s="1" t="inlineStr"/>
+      <c r="M23" s="1" t="inlineStr"/>
+      <c r="N23" s="1" t="inlineStr"/>
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="1" t="inlineStr"/>
+      <c r="Q23" s="1" t="inlineStr"/>
+      <c r="R23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr"/>
+      <c r="T23" s="1" t="inlineStr"/>
+      <c r="U23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" customHeight="1" ht="30">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Sofía Navarro Gil</t>
+          </r>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">55667788G</t>
+          </r>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">622000002</t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">sofia.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr"/>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" customHeight="1" ht="30">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Diego Castillo </t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99001122H</t>
+          </r>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">633000003</t>
+          </r>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">diego.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Baja</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr"/>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr"/>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" customHeight="1" ht="30">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
+          </r>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11223344F</t>
+          </r>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">611000001</t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javier.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr"/>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr"/>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" customHeight="1" ht="30">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Sofía Navarro Gil</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
+      <c r="F27" s="1" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">55667788G</t>
+          </r>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">622000002</t>
+          </r>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">sofia.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr"/>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" customHeight="1" ht="30">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Diego Castillo </t>
+          </r>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr"/>
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99001122H</t>
+          </r>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">633000003</t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">diego.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Baja</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr"/>
+      <c r="R28" s="7" t="inlineStr"/>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="7" t="inlineStr"/>
+      <c r="U28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" customHeight="1" ht="30">
+      <c r="A29" s="1" t="inlineStr"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr"/>
+      <c r="E29" s="1" t="inlineStr"/>
+      <c r="F29" s="1" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11223344F</t>
+          </r>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">611000001</t>
+          </r>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">javier.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">10/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q29" s="7" t="inlineStr"/>
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" customHeight="1" ht="30">
+      <c r="A30" s="1" t="inlineStr"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Sofía Navarro Gil</t>
+          </r>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr"/>
+      <c r="F30" s="1" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">55667788G</t>
+          </r>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">622000002</t>
+          </r>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">sofia.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">14/02/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Alta</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr"/>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr"/>
+      <c r="T30" s="7" t="inlineStr"/>
+      <c r="U30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" customHeight="1" ht="30">
+      <c r="A31" s="1" t="inlineStr"/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Diego Castillo </t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr"/>
+      <c r="F31" s="1" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99001122H</t>
+          </r>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">633000003</t>
+          </r>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">diego.</t>
+          </r>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Baja</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q31" s="7" t="inlineStr"/>
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr"/>
+      <c r="T31" s="7" t="inlineStr"/>
+      <c r="U31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" customHeight="1" ht="169">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr"/>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
+      <c r="L32" s="1" t="inlineStr"/>
+      <c r="M32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr"/>
+      <c r="O32" s="1" t="inlineStr"/>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" customHeight="1" ht="30">
+      <c r="A33" s="1" t="inlineStr"/>
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr"/>
+      <c r="D33" s="1" t="inlineStr"/>
+      <c r="E33" s="1" t="inlineStr"/>
+      <c r="F33" s="1" t="inlineStr"/>
+      <c r="G33" s="1" t="inlineStr"/>
+      <c r="H33" s="1" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr"/>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
+      <c r="L33" s="1" t="inlineStr"/>
+      <c r="M33" s="1" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2</t>
+          </r>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">/</t>
+          </r>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2</t>
+          </r>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr"/>
+      <c r="T33" s="8" t="inlineStr"/>
+      <c r="U33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" customHeight="1" ht="40">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr"/>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -974,8 +1815,82 @@
     <mergeCell ref="L14:M14"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="P14:T14"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:T15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:T16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:T17"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:T22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:T24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="P25:T25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:T26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="P27:T27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:T28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="P29:T29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="P30:T30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="P31:T31"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="R33:T33"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="landscape" paperSize="9"/>
